--- a/ACCY122/Tutorial/T02/T2.xlsx
+++ b/ACCY122/Tutorial/T02/T2.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2025 UOW\Learning Material\2025 Tutorials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Tutorial/T02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE7909F-A0F3-4ECF-97F4-5F7A97B5C3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E289FF-EDE7-C448-95E5-ADF13B359A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="802" firstSheet="1" activeTab="5" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18700" tabRatio="802" activeTab="5" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="4" r:id="rId1"/>
     <sheet name="System (2)" sheetId="5" r:id="rId2"/>
     <sheet name="Ex 3.5" sheetId="1" r:id="rId3"/>
-    <sheet name="Ex 3.13" sheetId="2" r:id="rId4"/>
-    <sheet name="P3.16" sheetId="3" r:id="rId5"/>
-    <sheet name="P3.17" sheetId="6" r:id="rId6"/>
-    <sheet name="ANSWERS" sheetId="7" r:id="rId7"/>
-    <sheet name="Ex 3.5 (2)" sheetId="8" r:id="rId8"/>
-    <sheet name="Ex 3.13 (2)" sheetId="9" r:id="rId9"/>
-    <sheet name="P3.17 (2)" sheetId="10" r:id="rId10"/>
-    <sheet name="P3.17 (3)" sheetId="11" r:id="rId11"/>
+    <sheet name="Ex 3.6" sheetId="13" r:id="rId4"/>
+    <sheet name="Ex 3.13" sheetId="2" r:id="rId5"/>
+    <sheet name="P3.16" sheetId="3" r:id="rId6"/>
+    <sheet name="P3.17" sheetId="6" r:id="rId7"/>
+    <sheet name="3.4" sheetId="12" r:id="rId8"/>
+    <sheet name="ANSWERS" sheetId="7" r:id="rId9"/>
+    <sheet name="Ex 3.5 (2)" sheetId="8" r:id="rId10"/>
+    <sheet name="Ex 3.13 (2)" sheetId="9" r:id="rId11"/>
+    <sheet name="P3.17 (2)" sheetId="10" r:id="rId12"/>
+    <sheet name="P3.17 (3)" sheetId="11" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="107">
   <si>
     <t>ASSETS</t>
   </si>
@@ -722,6 +724,21 @@
   <si>
     <t>Balance</t>
   </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>expense</t>
+  </si>
+  <si>
+    <t>asset</t>
+  </si>
+  <si>
+    <t>liability</t>
+  </si>
+  <si>
+    <t>equity</t>
+  </si>
 </sst>
 </file>
 
@@ -731,7 +748,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ 0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,6 +852,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Black"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1077,7 +1100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1182,81 +1205,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1297,8 +1261,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1025058" y="636227"/>
-          <a:ext cx="5375828" cy="5672912"/>
+          <a:off x="1088034" y="651971"/>
+          <a:ext cx="5942604" cy="5835598"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -2519,7 +2483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B31468-06B7-4EAE-81E5-FB432EF125CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2527,16 +2491,657 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CD0997-A444-4D69-AB73-C3039851DB20}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>37043</v>
+      </c>
+      <c r="B6" s="4">
+        <v>-620</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="3">
+        <v>-620</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>38504</v>
+      </c>
+      <c r="B7" s="4">
+        <v>-500</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>39965</v>
+      </c>
+      <c r="B8" s="4">
+        <v>-460</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3">
+        <v>-460</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>41791</v>
+      </c>
+      <c r="B9" s="4">
+        <v>-240</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-240</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>43252</v>
+      </c>
+      <c r="B10" s="4">
+        <v>-680</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="3">
+        <v>-680</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>44713</v>
+      </c>
+      <c r="B11" s="3">
+        <v>300</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-300</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11110</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="4">
+        <v>15000</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5FCBA2A-C3B9-48E4-A793-33D1A5662D02}">
+  <dimension ref="A5:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.5" customWidth="1"/>
+    <col min="7" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="15">
+        <v>2400</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="34">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="35">
+        <v>180</v>
+      </c>
+      <c r="G9" s="28">
+        <f>B9+E9-F9-F10</f>
+        <v>1670</v>
+      </c>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="34">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="35">
+        <v>550</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="16">
+        <v>530</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="36">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1670</v>
+      </c>
+      <c r="F11" s="35"/>
+      <c r="G11" s="30">
+        <f>B11+E11-F11</f>
+        <v>2200</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="18">
+        <v>8200</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="30">
+        <f t="shared" ref="G12:G13" si="0">B12+E12-F12</f>
+        <v>8200</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="18">
+        <v>420</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="30">
+        <f t="shared" si="0"/>
+        <v>420</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="23">
+        <v>2160</v>
+      </c>
+      <c r="D14" s="36">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>180</v>
+      </c>
+      <c r="F14" s="35"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="9">
+        <f>C14-E14+F14</f>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="24">
+        <v>2980</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="9">
+        <f t="shared" ref="H15:H17" si="1">C15-E15+F15</f>
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="24">
+        <v>4500</v>
+      </c>
+      <c r="D16" s="34">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="37">
+        <v>900</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="9">
+        <f t="shared" si="1"/>
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="24">
+        <v>6400</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="9">
+        <f t="shared" si="1"/>
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="16">
+        <v>6220</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="36">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>600</v>
+      </c>
+      <c r="F18" s="35"/>
+      <c r="G18" s="30">
+        <f>B18+E18-F18</f>
+        <v>6820</v>
+      </c>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="25">
+        <v>13800</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="9">
+        <f>C19-E19+F19</f>
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="16">
+        <v>5100</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="30">
+        <f>B20+E20-F20</f>
+        <v>5100</v>
+      </c>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="18">
+        <v>3200</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="30">
+        <f t="shared" ref="G21:G22" si="2">B21+E21-F21</f>
+        <v>3200</v>
+      </c>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="16">
+        <v>2950</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="30">
+        <f t="shared" si="2"/>
+        <v>2950</v>
+      </c>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="19">
+        <f>SUM(B9:B22)</f>
+        <v>29020</v>
+      </c>
+      <c r="C23" s="26">
+        <f>SUM(C9:C22)</f>
+        <v>29840</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="28">
+        <f>SUM(G9:G22)</f>
+        <v>30560</v>
+      </c>
+      <c r="H23" s="9">
+        <f>SUM(H9:H22)</f>
+        <v>30560</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D71950E-2CD7-4B78-893D-5069FC5F86D5}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -2559,7 +3164,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -2578,7 +3183,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -2612,7 +3217,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>98</v>
       </c>
@@ -2640,17 +3245,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C33730-14B6-4677-A48D-DB25619545D1}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -2673,7 +3278,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -2692,7 +3297,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -2726,7 +3331,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>98</v>
       </c>
@@ -2757,27 +3362,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6630C2FA-7F47-4646-A4FB-C656FFCA9DC7}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="41" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>48</v>
       </c>
@@ -2794,7 +3399,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="41" t="s">
         <v>52</v>
       </c>
@@ -2812,7 +3417,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C5" s="41"/>
       <c r="D5" s="41"/>
       <c r="E5" s="42" t="s">
@@ -2826,8 +3431,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C6" s="54" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C6" s="60" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="41"/>
@@ -2854,8 +3459,8 @@
       </c>
       <c r="O6" s="46"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C7" s="54"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C7" s="60"/>
       <c r="D7" s="41"/>
       <c r="E7" s="42" t="s">
         <v>57</v>
@@ -2867,8 +3472,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C8" s="54"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C8" s="60"/>
       <c r="D8" s="41"/>
       <c r="E8" s="41" t="s">
         <v>67</v>
@@ -2881,8 +3486,8 @@
       </c>
       <c r="O8" s="46"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C9" s="54"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C9" s="60"/>
       <c r="D9" s="41"/>
       <c r="E9" s="42" t="s">
         <v>57</v>
@@ -2890,8 +3495,8 @@
       <c r="M9" s="45"/>
       <c r="O9" s="46"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C10" s="54"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C10" s="60"/>
       <c r="D10" s="41"/>
       <c r="E10" s="41" t="s">
         <v>69</v>
@@ -2919,7 +3524,7 @@
       </c>
       <c r="O10" s="46"/>
     </row>
-    <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="41"/>
       <c r="D11" s="41"/>
       <c r="E11" s="41"/>
@@ -2939,7 +3544,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="41"/>
       <c r="D12" s="41"/>
       <c r="E12" s="42" t="s">
@@ -2956,7 +3561,7 @@
       </c>
       <c r="O12" s="46"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C13" s="41" t="s">
         <v>79</v>
       </c>
@@ -2973,7 +3578,7 @@
       <c r="M13" s="45"/>
       <c r="O13" s="46"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>82</v>
       </c>
@@ -2991,7 +3596,7 @@
       </c>
       <c r="O14" s="46"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M15" s="45" t="s">
         <v>84</v>
       </c>
@@ -2999,17 +3604,17 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M16" s="45" t="s">
         <v>85</v>
       </c>
       <c r="O16" s="46"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M17" s="45"/>
       <c r="O17" s="46"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
@@ -3024,7 +3629,7 @@
       </c>
       <c r="O18" s="46"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M19" s="45" t="s">
         <v>87</v>
       </c>
@@ -3032,7 +3637,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M20" s="51" t="s">
         <v>88</v>
       </c>
@@ -3053,259 +3658,302 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E30AB4-1E2F-415D-B46B-0954882CC2D5}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="58"/>
-    <col min="2" max="2" width="9.81640625" style="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" style="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="58"/>
-    <col min="5" max="5" width="4.81640625" style="58" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" style="58" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" style="58" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" style="58" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.08984375" style="58" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="58"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-    </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="57" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-    </row>
-    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A3" s="57" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="57" t="s">
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="57"/>
-    </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57" t="s">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A5" s="57" t="s">
+    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A6" s="59">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>37043</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A7" s="59">
+      <c r="B6" s="1">
+        <v>-620</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>-620</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>38504</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-    </row>
-    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A8" s="59">
+      <c r="B7" s="1">
+        <v>-500</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>39965</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57" t="s">
+      <c r="B8" s="1">
+        <v>-460</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <v>-460</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A9" s="59">
+    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>41791</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-    </row>
-    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A10" s="59">
+      <c r="B9" s="1">
+        <v>-240</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-240</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>43252</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57" t="s">
+      <c r="B10" s="1">
+        <v>-680</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>-680</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A11" s="59">
+    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>44713</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A12" s="59">
+      <c r="B11" s="1">
+        <v>300</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-300</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11110</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57" t="s">
+      <c r="B12" s="1">
+        <v>15000</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1">
+        <v>10500</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-    </row>
-    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-    </row>
-    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-    </row>
-    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
+    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3314,26 +3962,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55ECAF17-06F3-C246-9339-16CA7D6C2DCA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F37818-E825-4EA5-9082-388CE9393917}">
   <dimension ref="A5:H23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" customWidth="1"/>
-    <col min="7" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="3.5" customWidth="1"/>
+    <col min="7" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="56" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
@@ -3341,7 +3998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
@@ -3365,7 +4022,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>28</v>
       </c>
@@ -3377,11 +4034,15 @@
         <v>2</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="28"/>
+      <c r="F9" s="35">
+        <v>180</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1670</v>
+      </c>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="15"/>
       <c r="C10" s="21"/>
@@ -3389,11 +4050,13 @@
         <v>4</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="35"/>
+      <c r="F10" s="35">
+        <v>550</v>
+      </c>
       <c r="G10" s="29"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
@@ -3404,12 +4067,13 @@
       <c r="D11" s="36">
         <v>3</v>
       </c>
-      <c r="E11" s="1"/>
       <c r="F11" s="35"/>
-      <c r="G11" s="30"/>
+      <c r="G11" s="30">
+        <v>2200</v>
+      </c>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
@@ -3420,10 +4084,12 @@
       <c r="D12" s="36"/>
       <c r="E12" s="1"/>
       <c r="F12" s="35"/>
-      <c r="G12" s="30"/>
+      <c r="G12" s="30">
+        <v>8200</v>
+      </c>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>23</v>
       </c>
@@ -3434,10 +4100,12 @@
       <c r="D13" s="36"/>
       <c r="E13" s="1"/>
       <c r="F13" s="35"/>
-      <c r="G13" s="30"/>
+      <c r="G13" s="30">
+        <v>420</v>
+      </c>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>29</v>
       </c>
@@ -3448,12 +4116,16 @@
       <c r="D14" s="36">
         <v>2</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <v>180</v>
+      </c>
       <c r="F14" s="35"/>
       <c r="G14" s="29"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+      <c r="H14" s="9">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>30</v>
       </c>
@@ -3465,9 +4137,11 @@
       <c r="E15" s="1"/>
       <c r="F15" s="35"/>
       <c r="G15" s="29"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+      <c r="H15" s="9">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
@@ -3479,11 +4153,15 @@
         <v>1</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="37"/>
+      <c r="F16" s="37">
+        <v>900</v>
+      </c>
       <c r="G16" s="29"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+      <c r="H16" s="9">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>35</v>
       </c>
@@ -3495,9 +4173,11 @@
       <c r="E17" s="1"/>
       <c r="F17" s="35"/>
       <c r="G17" s="29"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+      <c r="H17" s="29">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
@@ -3508,12 +4188,16 @@
       <c r="D18" s="36">
         <v>5</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <v>600</v>
+      </c>
       <c r="F18" s="35"/>
-      <c r="G18" s="30"/>
+      <c r="G18" s="30">
+        <v>6820</v>
+      </c>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>24</v>
       </c>
@@ -3525,9 +4209,11 @@
       <c r="E19" s="1"/>
       <c r="F19" s="35"/>
       <c r="G19" s="29"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+      <c r="H19" s="9">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>32</v>
       </c>
@@ -3538,10 +4224,12 @@
       <c r="D20" s="36"/>
       <c r="E20" s="1"/>
       <c r="F20" s="35"/>
-      <c r="G20" s="30"/>
+      <c r="G20" s="30">
+        <v>5100</v>
+      </c>
       <c r="H20" s="10"/>
     </row>
-    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>25</v>
       </c>
@@ -3552,10 +4240,12 @@
       <c r="D21" s="36"/>
       <c r="E21" s="1"/>
       <c r="F21" s="35"/>
-      <c r="G21" s="30"/>
+      <c r="G21" s="30">
+        <v>3200</v>
+      </c>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>26</v>
       </c>
@@ -3566,10 +4256,12 @@
       <c r="D22" s="36"/>
       <c r="E22" s="1"/>
       <c r="F22" s="35"/>
-      <c r="G22" s="30"/>
+      <c r="G22" s="30">
+        <v>2950</v>
+      </c>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14"/>
       <c r="B23" s="19">
         <f>SUM(B9:B22)</f>
@@ -3582,8 +4274,14 @@
       <c r="D23" s="38"/>
       <c r="E23" s="39"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="9"/>
+      <c r="G23" s="57">
+        <f>SUM(G9:G22)</f>
+        <v>30560</v>
+      </c>
+      <c r="H23" s="58">
+        <f>SUM(H9:H22)</f>
+        <v>30560</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3591,24 +4289,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{447D417B-E426-4079-AF68-C1412C0A3C5C}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,7 +4325,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3644,7 +4342,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>17</v>
@@ -3668,7 +4366,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -3691,7 +4389,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -3728,7 +4426,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3752,38 +4450,50 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
+      <c r="B7" s="1">
+        <v>120000</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1">
+        <v>120000</v>
+      </c>
+      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
+      <c r="B8" s="1">
+        <v>-1800</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
+        <v>-1800</v>
+      </c>
       <c r="K8" s="1" t="s">
         <v>89</v>
       </c>
@@ -3792,57 +4502,77 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>3</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
+      <c r="B9" s="1">
+        <v>-32000</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1">
+        <v>70000</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1">
+        <v>38000</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>4</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
+      <c r="B10" s="1">
+        <v>-8400</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <v>8400</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
+      <c r="B11" s="1">
+        <v>-1230</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>-1230</v>
+      </c>
       <c r="K11" s="1" t="s">
         <v>90</v>
       </c>
@@ -3851,19 +4581,27 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>16</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
+      <c r="B12" s="1">
+        <v>3250</v>
+      </c>
+      <c r="C12" s="1">
+        <v>620</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>3870</v>
+      </c>
       <c r="K12" s="1" t="s">
         <v>64</v>
       </c>
@@ -3872,19 +4610,25 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
+      <c r="B13" s="1">
+        <v>-480</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>-480</v>
+      </c>
       <c r="K13" s="1" t="s">
         <v>91</v>
       </c>
@@ -3893,57 +4637,78 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>23</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
+      <c r="B14" s="1">
+        <v>200</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>200</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>28</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
+      <c r="B15" s="1">
+        <v>-560</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1">
+        <v>-560</v>
+      </c>
+      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>31</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
+      <c r="B16" s="1">
+        <v>3680</v>
+      </c>
+      <c r="C16" s="1">
+        <v>580</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <f>B16+C16</f>
+        <v>4260</v>
+      </c>
       <c r="K16" s="1" t="s">
         <v>64</v>
       </c>
@@ -3952,19 +4717,25 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>31</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
+      <c r="B17" s="1">
+        <v>-440</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>-440</v>
+      </c>
       <c r="K17" s="1" t="s">
         <v>93</v>
       </c>
@@ -3973,60 +4744,62 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="1">
         <f>SUM(B7:B18)</f>
-        <v>0</v>
+        <v>82220</v>
       </c>
       <c r="C19" s="1">
         <f>SUM(C7:C18)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="D19" s="1">
         <f>SUM(D7:D18)</f>
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E19" s="1">
         <f>SUM(E7:E18)</f>
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="1">
         <f>SUM(G7:G18)</f>
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I19" s="1">
         <f>SUM(I7:I18)</f>
-        <v>0</v>
+        <v>119440</v>
       </c>
       <c r="J19" s="1">
         <f>SUM(J7:J18)</f>
-        <v>0</v>
+        <v>4380</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -4034,32 +4807,32 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="55">
+      <c r="B20" s="59">
         <f>SUM(B19:E19)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
+        <v>161820</v>
+      </c>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
       <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="59">
         <f>SUM(G19:J19)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
+        <v>161820</v>
+      </c>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4076,7 +4849,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4093,7 +4866,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4110,7 +4883,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4127,7 +4900,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4144,7 +4917,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4161,7 +4934,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4178,7 +4951,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4195,7 +4968,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4212,7 +4985,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4229,7 +5002,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4246,7 +5019,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4263,7 +5036,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -4280,7 +5053,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="17" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:15" ht="17" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -4308,55 +5081,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24344DF0-6919-4FB3-9F02-3A7703812720}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.90625" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="55" t="s">
         <v>18</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="60" t="s">
+      <c r="H1" s="56"/>
+      <c r="I1" s="54" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
     </row>
-    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="62"/>
+      <c r="G2" s="56"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
         <v>39</v>
@@ -4364,7 +5137,7 @@
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
     </row>
-    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>100</v>
       </c>
@@ -4397,8 +5170,8 @@
       </c>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A4" s="62"/>
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A4" s="56"/>
       <c r="B4" s="10" t="s">
         <v>98</v>
       </c>
@@ -4420,232 +5193,232 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A5" s="62"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
       <c r="E5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-    </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+    </row>
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-    </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+    </row>
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-    </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A8" s="62"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+    </row>
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8" s="56"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-    </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A9" s="62"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+    </row>
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-    </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A10" s="62"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+    </row>
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-    </row>
-    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A11" s="62"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+    </row>
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-    </row>
-    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+    </row>
+    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-    </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A13" s="62"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+    </row>
+    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-    </row>
-    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A14" s="62"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+    </row>
+    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="56"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-    </row>
-    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A15" s="62"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+    </row>
+    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-    </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A16" s="62"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+    </row>
+    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
-    </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A17" s="62"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+    </row>
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-    </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+    </row>
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
       <c r="E18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.5">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
       <c r="E19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-    </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="56"/>
+    </row>
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -4685,7 +5458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D22">
         <f>SUM(B20:D20)</f>
         <v>0</v>
@@ -4700,652 +5473,96 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E3D6BC-EBCC-4192-91D8-66369F108705}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61509360-8542-1F4D-9393-598DCE3CBA95}">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CD0997-A444-4D69-AB73-C3039851DB20}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.81640625" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A6" s="2">
-        <v>37043</v>
-      </c>
-      <c r="B6" s="4">
-        <v>-620</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="3">
-        <v>-620</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A7" s="2">
-        <v>38504</v>
-      </c>
-      <c r="B7" s="4">
-        <v>-500</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2500</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A8" s="2">
-        <v>39965</v>
-      </c>
-      <c r="B8" s="4">
-        <v>-460</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="3">
-        <v>-460</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A9" s="2">
-        <v>41791</v>
-      </c>
-      <c r="B9" s="4">
-        <v>-240</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-240</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A10" s="2">
-        <v>43252</v>
-      </c>
-      <c r="B10" s="4">
-        <v>-680</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="3">
-        <v>-680</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A11" s="2">
-        <v>44713</v>
-      </c>
-      <c r="B11" s="3">
-        <v>300</v>
-      </c>
-      <c r="C11" s="1">
-        <v>-300</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A12" s="2">
-        <v>11110</v>
-      </c>
-      <c r="B12" s="3">
-        <v>10500</v>
-      </c>
-      <c r="C12" s="3">
-        <v>4500</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="4">
-        <v>15000</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.5">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-  </sheetData>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E3D6BC-EBCC-4192-91D8-66369F108705}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5FCBA2A-C3B9-48E4-A793-33D1A5662D02}">
-  <dimension ref="A5:H23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" customWidth="1"/>
-    <col min="7" max="8" width="9.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="15">
-        <v>2400</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="34">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="35">
-        <v>180</v>
-      </c>
-      <c r="G9" s="28">
-        <f>B9+E9-F9-F10</f>
-        <v>1670</v>
-      </c>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A10" s="13"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="34">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="35">
-        <v>550</v>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="16">
-        <v>530</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="36">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1670</v>
-      </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="30">
-        <f>B11+E11-F11</f>
-        <v>2200</v>
-      </c>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="18">
-        <v>8200</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="30">
-        <f t="shared" ref="G12:G13" si="0">B12+E12-F12</f>
-        <v>8200</v>
-      </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A13" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="18">
-        <v>420</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="30">
-        <f t="shared" si="0"/>
-        <v>420</v>
-      </c>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="23">
-        <v>2160</v>
-      </c>
-      <c r="D14" s="36">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>180</v>
-      </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="9">
-        <f>C14-E14+F14</f>
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A15" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="24">
-        <v>2980</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="9">
-        <f t="shared" ref="H15:H17" si="1">C15-E15+F15</f>
-        <v>2980</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="24">
-        <v>4500</v>
-      </c>
-      <c r="D16" s="34">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="37">
-        <v>900</v>
-      </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="9">
-        <f t="shared" si="1"/>
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A17" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="24">
-        <v>6400</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="9">
-        <f t="shared" si="1"/>
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="16">
-        <v>6220</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="36">
-        <v>5</v>
-      </c>
-      <c r="E18" s="1">
-        <v>600</v>
-      </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="30">
-        <f>B18+E18-F18</f>
-        <v>6820</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="25">
-        <v>13800</v>
-      </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="9">
-        <f>C19-E19+F19</f>
-        <v>13800</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A20" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="16">
-        <v>5100</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="30">
-        <f>B20+E20-F20</f>
-        <v>5100</v>
-      </c>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A21" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="18">
-        <v>3200</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="30">
-        <f t="shared" ref="G21:G22" si="2">B21+E21-F21</f>
-        <v>3200</v>
-      </c>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.5">
-      <c r="A22" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="16">
-        <v>2950</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="30">
-        <f t="shared" si="2"/>
-        <v>2950</v>
-      </c>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="14"/>
-      <c r="B23" s="19">
-        <f>SUM(B9:B22)</f>
-        <v>29020</v>
-      </c>
-      <c r="C23" s="26">
-        <f>SUM(C9:C22)</f>
-        <v>29840</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="28">
-        <f>SUM(G9:G22)</f>
-        <v>30560</v>
-      </c>
-      <c r="H23" s="9">
-        <f>SUM(H9:H22)</f>
-        <v>30560</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>